--- a/Documentation/Week 8/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 8/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 8/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="280" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05F5FEB3-B30A-41BD-A1F7-A6DC25DC3A80}"/>
+  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07A545EE-BE6E-47F8-832F-80F2CD58BF75}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="10008" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="34">
   <si>
     <t>Wk</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>Retrospective Documentation</t>
+  </si>
+  <si>
+    <t>CycloneDDS Mujoco running documentation</t>
   </si>
 </sst>
 </file>
@@ -378,6 +381,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -396,14 +407,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -841,36 +844,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
@@ -890,7 +893,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1760,14 +1763,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2125,21 +2128,35 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B43" s="4"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="5"/>
-      <c r="G43" s="6" t="str">
+      <c r="A43" s="1">
+        <v>8</v>
+      </c>
+      <c r="B43" s="4">
+        <v>44816</v>
+      </c>
+      <c r="C43" s="5">
+        <v>0.8125</v>
+      </c>
+      <c r="D43" s="4">
+        <v>44816</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H43" s="1" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+      <c r="H43" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>35.749999999883585</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.50000000005820766</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
@@ -2509,14 +2526,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -3005,14 +3022,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3499,18 +3516,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3524,6 +3529,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 8/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 8/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 8/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07A545EE-BE6E-47F8-832F-80F2CD58BF75}"/>
+  <xr:revisionPtr revIDLastSave="293" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC00BA79-ADE5-4B90-86A7-C644163E6059}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="10008" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="16440" windowHeight="28320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
   <si>
     <t>Wk</t>
   </si>
@@ -381,14 +381,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -407,6 +399,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -829,55 +829,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.90625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64.08984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.6328125" style="1"/>
+    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
-    </row>
-    <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="16"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1759,18 +1759,18 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>2</v>
@@ -2160,21 +2160,35 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B44" s="4"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="5"/>
-      <c r="G44" s="6" t="str">
+      <c r="A44" s="1">
+        <v>8</v>
+      </c>
+      <c r="B44" s="4">
+        <v>44818</v>
+      </c>
+      <c r="C44" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="D44" s="4">
+        <v>44818</v>
+      </c>
+      <c r="E44" s="5">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H44" s="1" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+      <c r="H44" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>36.249999999941792</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.50000000005820766</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
@@ -2522,18 +2536,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2548,7 +2562,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>2</v>
@@ -3018,18 +3032,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="11"/>
-      <c r="D99" s="10" t="s">
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3044,7 +3058,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>2</v>
@@ -3516,6 +3530,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3529,18 +3555,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -3552,7 +3566,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3564,7 +3578,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Documentation/Week 8/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 8/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 8/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="293" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC00BA79-ADE5-4B90-86A7-C644163E6059}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20480C6E-CE5D-4480-BCE8-79024D78919A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="16440" windowHeight="28320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="35">
   <si>
     <t>Wk</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>CycloneDDS Mujoco running documentation</t>
+  </si>
+  <si>
+    <t>Client meeting Prep (documentation)</t>
   </si>
 </sst>
 </file>
@@ -381,6 +384,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -399,14 +410,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -844,36 +847,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
@@ -893,7 +896,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1763,14 +1766,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2192,57 +2195,96 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B45" s="4"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="5"/>
-      <c r="G45" s="6" t="str">
+      <c r="A45" s="1">
+        <v>8</v>
+      </c>
+      <c r="B45" s="4">
+        <v>44819</v>
+      </c>
+      <c r="C45" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D45" s="4">
+        <v>44819</v>
+      </c>
+      <c r="E45" s="5">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H45" s="1" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="H45" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>36.999999999941792</v>
       </c>
       <c r="I45" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B46" s="4"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="5"/>
-      <c r="G46" s="6" t="str">
+      <c r="A46" s="1">
+        <v>8</v>
+      </c>
+      <c r="B46" s="4">
+        <v>44819</v>
+      </c>
+      <c r="C46" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D46" s="4">
+        <v>44819</v>
+      </c>
+      <c r="E46" s="5">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H46" s="1" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+      <c r="H46" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>37.5</v>
       </c>
       <c r="I46" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.50000000005820766</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B47" s="4"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="5"/>
-      <c r="G47" s="6" t="str">
+      <c r="A47" s="1">
+        <v>8</v>
+      </c>
+      <c r="B47" s="4">
+        <v>44819</v>
+      </c>
+      <c r="C47" s="5">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D47" s="4">
+        <v>44819</v>
+      </c>
+      <c r="E47" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="G47" s="6">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H47" s="1" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+      <c r="H47" s="1">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v>38.000000000058208</v>
       </c>
       <c r="I47" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.50000000005820766</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
@@ -2540,14 +2582,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -3036,14 +3078,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3530,18 +3572,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3555,6 +3585,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 8/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 8/Booked Hours/Booked_Hours_Christo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 8/Booked Hours/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 8/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20480C6E-CE5D-4480-BCE8-79024D78919A}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9062E1E3-8E3F-4203-8854-01F37DF1CA05}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="36">
   <si>
     <t>Wk</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>Client meeting Prep (documentation)</t>
+  </si>
+  <si>
+    <t>Client Meeting</t>
   </si>
 </sst>
 </file>
@@ -505,10 +508,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -832,21 +831,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.625" style="1"/>
+    <col min="1" max="1" width="5.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.08984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
@@ -858,7 +857,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="14"/>
     </row>
-    <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -880,7 +879,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1762,7 +1761,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
@@ -1788,7 +1787,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>2</v>
@@ -2273,6 +2272,9 @@
       </c>
       <c r="E47" s="5">
         <v>0.5625</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="G47" s="6">
         <f t="shared" si="3"/>
@@ -2578,7 +2580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
@@ -2604,7 +2606,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>2</v>
@@ -3074,7 +3076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
@@ -3100,7 +3102,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>2</v>
@@ -3608,7 +3610,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3620,7 +3622,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
